--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487831_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487831_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7797</v>
+        <v>6.2865</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9046</v>
+        <v>4.5582</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8751</v>
+        <v>1.7283</v>
       </c>
       <c r="G2" t="n">
         <v>4.3371</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7507</v>
+        <v>2.2575</v>
       </c>
       <c r="T2" t="n">
-        <v>2.618</v>
+        <v>1.2716</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1327</v>
+        <v>0.9859</v>
       </c>
       <c r="V2" t="n">
         <v>1.9813</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1155</v>
+        <v>3.5866</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4969</v>
+        <v>4.056</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3814</v>
+        <v>-0.4694</v>
       </c>
       <c r="G3" t="n">
         <v>1.8142</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2388</v>
+        <v>0.2323</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2238</v>
+        <v>0.3353</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.015</v>
+        <v>-0.103</v>
       </c>
       <c r="V3" t="n">
         <v>0.7076</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5267</v>
+        <v>2.8953</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06900000000000001</v>
+        <v>4.1496</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5957</v>
+        <v>-1.2543</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1419</v>
+        <v>4.4809</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1534</v>
+        <v>1.8276</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0114</v>
+        <v>2.6534</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0523</v>
+        <v>5.1627</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6392</v>
+        <v>0.9786</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4131</v>
+        <v>4.1842</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0897</v>
+        <v>-0.6818</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5142</v>
+        <v>0.849</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4245</v>
+        <v>-1.5308</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4568</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1517</v>
+        <v>-0.337</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2701</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8816</v>
+        <v>-0.2374</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6899</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6899</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3221</v>
+        <v>2.572</v>
       </c>
       <c r="E5" t="n">
-        <v>3.87</v>
+        <v>2.1934</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5479</v>
+        <v>0.3787</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4809</v>
+        <v>-0.8075</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8276</v>
+        <v>0.013</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6534</v>
+        <v>-0.8205</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1627</v>
+        <v>-0.5299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9786</v>
+        <v>-0.5992</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1842</v>
+        <v>0.0694</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6818</v>
+        <v>-0.2777</v>
       </c>
       <c r="N5" t="n">
-        <v>0.849</v>
+        <v>0.6122</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5308</v>
+        <v>-0.8899</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9101</v>
+        <v>0.212</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3791</v>
+        <v>0.3882</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.531</v>
+        <v>-0.1761</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9901</v>
+        <v>2.1566</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6995</v>
+        <v>0.383</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2906</v>
+        <v>1.7736</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8075</v>
+        <v>1.1419</v>
       </c>
       <c r="H6" t="n">
-        <v>0.013</v>
+        <v>1.1534</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8205</v>
+        <v>-0.0114</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5299</v>
+        <v>1.0523</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5992</v>
+        <v>0.6392</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0694</v>
+        <v>0.4131</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2777</v>
+        <v>0.0897</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6122</v>
+        <v>0.5142</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8899</v>
+        <v>-0.4245</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3699</v>
+        <v>1.7816</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1057</v>
+        <v>0.722</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2642</v>
+        <v>1.0596</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3351</v>
+        <v>0.6899</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3351</v>
+        <v>0.6899</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2713</v>
+        <v>0.8831</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1887</v>
+        <v>-0.6062</v>
       </c>
       <c r="F7" t="n">
-        <v>1.46</v>
+        <v>1.4894</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2854</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6192</v>
+        <v>1.231</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1214</v>
+        <v>0.461</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7405</v>
+        <v>0.7699</v>
       </c>
       <c r="V7" t="n">
         <v>0.3538</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0179</v>
+        <v>-0.0431</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7211</v>
+        <v>-1.8702</v>
       </c>
       <c r="F8" t="n">
-        <v>1.739</v>
+        <v>1.8271</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2955</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3727</v>
+        <v>1.3117</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7763</v>
+        <v>0.6272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5964</v>
+        <v>0.6844</v>
       </c>
       <c r="V8" t="n">
         <v>1.3975</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0805</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.575</v>
+        <v>-0.5098</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4946</v>
+        <v>0.4359</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5322</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6381</v>
+        <v>0.6446</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.7392</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0358</v>
+        <v>-0.0946</v>
       </c>
       <c r="V9" t="n">
         <v>0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4602</v>
+        <v>-0.2966</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4331</v>
+        <v>-0.475</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0271</v>
+        <v>0.1784</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4886</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0065</v>
+        <v>0.1701</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4129</v>
+        <v>0.371</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4064</v>
+        <v>-0.2009</v>
       </c>
       <c r="V10" t="n">
         <v>0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0509</v>
+        <v>-2.2298</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1334</v>
+        <v>-1.7234</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9175</v>
+        <v>-0.5064</v>
       </c>
       <c r="G11" t="n">
         <v>-1.343</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2479</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0562</v>
+        <v>0.3539</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1918</v>
+        <v>0.2193</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0437</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.4317</v>
+        <v>15.7367</v>
       </c>
       <c r="E12" t="n">
-        <v>8.850700000000002</v>
+        <v>10.1556</v>
       </c>
       <c r="F12" t="n">
-        <v>5.581100000000001</v>
+        <v>5.5813</v>
       </c>
       <c r="G12" t="n">
         <v>7.0219</v>
@@ -1360,13 +1360,13 @@
         <v>11.4716</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.449400000000001</v>
+        <v>-4.449399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>9.084700000000002</v>
+        <v>9.0847</v>
       </c>
       <c r="K12" t="n">
-        <v>3.227199999999999</v>
+        <v>3.2272</v>
       </c>
       <c r="L12" t="n">
         <v>5.8578</v>
@@ -1390,16 +1390,16 @@
         <v>7.2845</v>
       </c>
       <c r="S12" t="n">
-        <v>6.7722</v>
+        <v>8.076899999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>3.865</v>
+        <v>5.169900000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.907</v>
+        <v>2.9071</v>
       </c>
       <c r="V12" t="n">
-        <v>6.8815</v>
+        <v>6.881500000000001</v>
       </c>
       <c r="W12" t="n">
         <v>9.428800000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9989</v>
+        <v>2.7045</v>
       </c>
       <c r="E13" t="n">
-        <v>2.153</v>
+        <v>2.3673</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1541</v>
+        <v>0.3372</v>
       </c>
       <c r="G13" t="n">
         <v>0.6469</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3231</v>
+        <v>-0.6175</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9167</v>
+        <v>-0.7024</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4064</v>
+        <v>0.0849</v>
       </c>
       <c r="V13" t="n">
         <v>1.6345</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1865</v>
+        <v>1.7159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7556</v>
+        <v>0.9699</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4309</v>
+        <v>0.746</v>
       </c>
       <c r="G14" t="n">
         <v>0.6361</v>
@@ -1546,13 +1546,13 @@
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6578</v>
+        <v>-1.1283</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9525</v>
+        <v>-0.6374</v>
       </c>
       <c r="V14" t="n">
         <v>1.1675</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8829</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="E15" t="n">
         <v>1.6993</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8163</v>
+        <v>-0.7028</v>
       </c>
       <c r="G15" t="n">
         <v>0.9678</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3314</v>
+        <v>0.4449</v>
       </c>
       <c r="T15" t="n">
         <v>0.3882</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0567</v>
+        <v>0.0568</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4228</v>
+        <v>0.4522</v>
       </c>
       <c r="E16" t="n">
         <v>0.5873</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1645</v>
+        <v>-0.1351</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0254</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3843</v>
+        <v>-0.3549</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1181</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2662</v>
+        <v>-0.2368</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4638</v>
+        <v>-0.1741</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0468</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.417</v>
+        <v>-0.1273</v>
       </c>
       <c r="G17" t="n">
         <v>0.6094000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.657</v>
+        <v>-0.3673</v>
       </c>
       <c r="T17" t="n">
         <v>0.1924</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8494</v>
+        <v>-0.5597</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5841</v>
+        <v>-0.431</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0961</v>
+        <v>-0.011</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6802</v>
+        <v>-0.4199</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4653</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1031</v>
+        <v>0.2562</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1396</v>
+        <v>0.0324</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0365</v>
+        <v>0.2238</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0543</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6302</v>
+        <v>-0.8245</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0611</v>
+        <v>0.1683</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6913</v>
+        <v>-0.9927</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1409</v>
@@ -1936,13 +1936,13 @@
         <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8044</v>
+        <v>-0.9987</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9943</v>
+        <v>-0.8872</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1899</v>
+        <v>-0.1115</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9742</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5995</v>
+        <v>-1.0573</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0895</v>
+        <v>0.5181</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6889</v>
+        <v>-1.5754</v>
       </c>
       <c r="G20" t="n">
         <v>0.1082</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2153</v>
+        <v>0.3268</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.55</v>
+        <v>-0.1214</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3347</v>
+        <v>0.4482</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2843</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5982</v>
+        <v>-2.3991</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4257</v>
+        <v>-2.7471</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1726</v>
+        <v>0.348</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6035</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4993</v>
+        <v>-1.3001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3981</v>
+        <v>-0.7195</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1012</v>
+        <v>-0.5806</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5767</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2494</v>
+        <v>-5.0771</v>
       </c>
       <c r="E22" t="n">
         <v>-4.8991</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3503</v>
+        <v>-0.1781</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9797</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4373</v>
+        <v>-1.265</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4848</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9525</v>
+        <v>-0.7802</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7978</v>
+        <v>-8.194599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6514</v>
+        <v>-4.1872</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1464</v>
+        <v>-4.0075</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7756</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7718</v>
+        <v>0.3749</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5401</v>
+        <v>0.0043</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2317</v>
+        <v>0.3706</v>
       </c>
       <c r="V23" t="n">
         <v>-4.7939</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.4319</v>
+        <v>-12.2886</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.581099999999999</v>
+        <v>-5.581</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.8507</v>
+        <v>-6.707600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-7.021999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>13.5279</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.772200000000001</v>
+        <v>-4.629</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.906999999999999</v>
+        <v>-2.9071</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8651</v>
+        <v>-1.7219</v>
       </c>
       <c r="V24" t="n">
         <v>-6.881399999999999</v>
